--- a/data/dados_sisor_2027/base_detalhamento_obras.xlsx
+++ b/data/dados_sisor_2027/base_detalhamento_obras.xlsx
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>60000</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>197857</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>1929103</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>1929103</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>41022</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>100000</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>280106</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>519640</v>
+        <v>799746</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -5460,10 +5460,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>894720</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4087644</v>
+        <v>4982364</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>8264640</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>19153735</v>
+        <v>27418375</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -5596,10 +5596,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>3155040</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>23943007</v>
+        <v>27098047</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>4840800</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>26593690</v>
+        <v>31434490</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>613500</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2870210</v>
+        <v>3483710</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>5963400</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>23280000</v>
+        <v>29243400</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>3620820</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>19100000</v>
+        <v>22720820</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>1839798</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3269655</v>
+        <v>5109453</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
         <v>222899</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
         <v>299895</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
         <v>4565604</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
       </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>6286532</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2728583</v>
+        <v>9015115</v>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
         <v>193263</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>904245</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>44308050</v>
+        <v>45212295</v>
       </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
         <v>6999284</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
       </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
         <v>651694</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
       </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
         <v>651694</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
       </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
         <v>1472757</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
         <v>651694</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
       </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
         <v>18572878</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>19850000</v>
+        <v>20000000</v>
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
         <v>350000</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
       </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
       </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
         <v>143000</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
       </c>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
@@ -9958,10 +9958,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
         <v>5876140</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
       </c>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
         <v>1132500</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
       </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
@@ -10090,10 +10090,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
         <v>34710000</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
       </c>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
@@ -10156,10 +10156,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
         <v>59000000</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
       </c>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
       </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
         <v>200000</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0</v>
       </c>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
         <v>30980000</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
       </c>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr"/>
@@ -10420,10 +10420,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
         <v>25655000</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0</v>
       </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
         <v>66560000</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0</v>
       </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
         <v>25464500</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0</v>
       </c>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
@@ -10618,10 +10618,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
         <v>1202905</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
       </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0</v>
       </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
@@ -10750,10 +10750,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
         <v>14920000</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
       </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
         <v>8798400</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0</v>
       </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
@@ -10882,10 +10882,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0</v>
       </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
@@ -10948,10 +10948,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
         <v>1203643</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
       </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
         <v>66620</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0</v>
       </c>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
@@ -11080,10 +11080,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
       </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
@@ -11146,10 +11146,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
         <v>2940000</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
       </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
@@ -11212,10 +11212,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
       </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
@@ -11278,10 +11278,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
         <v>542000</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
       </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
@@ -11344,10 +11344,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
         <v>2163814</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
       </c>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
@@ -11410,10 +11410,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
         <v>11974837</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
       </c>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
@@ -11476,10 +11476,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
         <v>1382535</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0</v>
       </c>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
@@ -11542,10 +11542,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0</v>
       </c>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
@@ -11608,10 +11608,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
         <v>35359853</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0</v>
       </c>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
@@ -11674,10 +11674,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
         <v>13982612</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
       </c>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
@@ -11740,10 +11740,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0</v>
       </c>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
@@ -11806,10 +11806,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
         <v>10459632</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
       </c>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
         <v>17000000</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0</v>
       </c>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
@@ -11938,10 +11938,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
         <v>74941121</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0</v>
       </c>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr"/>
@@ -12004,10 +12004,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
         <v>38460000</v>
-      </c>
-      <c r="R171" t="n">
-        <v>0</v>
       </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
@@ -12070,10 +12070,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R172" t="n">
-        <v>0</v>
       </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
@@ -12136,10 +12136,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
         <v>7000000</v>
-      </c>
-      <c r="R173" t="n">
-        <v>0</v>
       </c>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R174" t="n">
-        <v>0</v>
       </c>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
         <v>100000</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
       </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
@@ -12862,10 +12862,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
         <v>6121132</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0</v>
       </c>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
         <v>3541728</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0</v>
       </c>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
@@ -12994,10 +12994,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
         <v>22254062</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
       </c>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
@@ -13060,10 +13060,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0</v>
       </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
@@ -13126,10 +13126,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0</v>
       </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
@@ -13192,10 +13192,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
         <v>431809</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0</v>
       </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
@@ -13258,10 +13258,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0</v>
       </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
@@ -13324,10 +13324,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="n">
         <v>14356790</v>
-      </c>
-      <c r="R191" t="n">
-        <v>0</v>
       </c>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
@@ -13390,10 +13390,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
         <v>1000</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
       </c>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
@@ -13456,10 +13456,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
         <v>1000</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
       </c>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
@@ -13984,10 +13984,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
         <v>50000000</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0</v>
       </c>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
@@ -14050,10 +14050,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
         <v>8151612</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0</v>
       </c>
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr"/>
@@ -14116,10 +14116,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
+        <v>0</v>
+      </c>
+      <c r="R203" t="n">
         <v>7488179</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
       </c>
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr"/>
@@ -14182,10 +14182,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
         <v>9608804</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0</v>
       </c>
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr"/>
@@ -14248,10 +14248,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
         <v>8168067</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0</v>
       </c>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
+        <v>0</v>
+      </c>
+      <c r="R206" t="n">
         <v>571386707</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0</v>
       </c>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr"/>
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
         <v>15000000</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
       </c>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr"/>
@@ -14446,10 +14446,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
         <v>1406178</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
       </c>
       <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr"/>
@@ -14512,10 +14512,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
         <v>19448656</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
       </c>
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr"/>
@@ -14578,10 +14578,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
       </c>
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr"/>
@@ -14644,10 +14644,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
         <v>30000000</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0</v>
       </c>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
@@ -14710,10 +14710,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
       </c>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr"/>
@@ -14776,10 +14776,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
         <v>4000000</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
       </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr"/>
@@ -14842,10 +14842,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
         <v>4000000</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0</v>
       </c>
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr"/>
@@ -14908,10 +14908,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
         <v>1000000</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0</v>
       </c>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr"/>
@@ -15312,10 +15312,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
         <v>8311374</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
       </c>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
@@ -15378,10 +15378,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
         <v>477508</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
       </c>
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr"/>
